--- a/docs/PPG/Produção.xlsx
+++ b/docs/PPG/Produção.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A418B65F-5BC7-FF48-9951-11273A71A46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5372D6-2E9C-184E-A973-32F92997AD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="680" windowWidth="29240" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="artigos-completos" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="1564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="1600">
   <si>
     <t>Aceito</t>
   </si>
@@ -4650,9 +4650,6 @@
     <t>FATIGUE IN LONG COVID: AN EXPLORATORY PRAGMATIC RANDOMIZED TRIAL OF OSTEOPATHIC CARE PLUS PHYSICAL THERAPY VERSUS PHYSICAL THERAPY ALONE</t>
   </si>
   <si>
-    <t>DISEASE SEVERITY AND ITS ASSOCIATIONS WITH NON-ATAXIC SIGNS, COGNITION, MOBILITY, AND BALANCE IN SPINOCEREBELLAR ATAXIA: A CROSS-SECTIONAL STUDY: SCA SEVERITY AND OUTCOMES</t>
-  </si>
-  <si>
     <t>10.20945/2359-4292-2026-0036</t>
   </si>
   <si>
@@ -4677,9 +4674,6 @@
     <t>10.1016/j.jorep.2026.101049</t>
   </si>
   <si>
-    <t>Hand preference does not impact upright posture control during a reaching and grasping task: A cross-sectional study in healthy women</t>
-  </si>
-  <si>
     <t>10.1177/19433654261447876</t>
   </si>
   <si>
@@ -4707,9 +4701,6 @@
     <t>10.12688/f1000research.180073.1</t>
   </si>
   <si>
-    <t>Effect of high-intensity interval training (HIIT) versus moderate-intensity continuous training (MICT) on insulin sensitivity in participants with type 2 diabetes mellitus (T2DM): A systematic review and meta-analysis of randomised controlled trials [version 1; peer review: awaiting peer review</t>
-  </si>
-  <si>
     <t>Translation, cross-cultural adaptation, and measurement properties of the Back pain knowledge and beliefs survey (BacKS) for the Brazilian population</t>
   </si>
   <si>
@@ -4738,6 +4729,123 @@
   </si>
   <si>
     <t>Temporal trends (2006-2019) regarding physical activity among adolescents living in the city of Rio de Janeiro, Brazil</t>
+  </si>
+  <si>
+    <t>A Comparison of Acute Responses to Isometric and Dynamic Resistance Training Matched for External Load, Number of Sets, and Time Under Tension in Recreationally Trained Subjects</t>
+  </si>
+  <si>
+    <t>10.1177/10519815261464557</t>
+  </si>
+  <si>
+    <t>Disease Severity and Its Associations With Non-Ataxic Signs, Cognition, Mobility, and Balance In Spinocerebellar Ataxia: A Cross-Sectional Study</t>
+  </si>
+  <si>
+    <t>10.46979/rbn.v62i2.72063</t>
+  </si>
+  <si>
+    <t>10.1177/09612033261461973</t>
+  </si>
+  <si>
+    <t>10.3390/healthcare14121723</t>
+  </si>
+  <si>
+    <t>10.47197/retos.v82.119417</t>
+  </si>
+  <si>
+    <t>10.1590/1809-2950/e23009326en</t>
+  </si>
+  <si>
+    <t>Association between Physical Function, Pulmonary Function, and Social Determinants of Health in Individuals with Post-Tuberculosis Lung Disease</t>
+  </si>
+  <si>
+    <t>10.3390/arm94040052</t>
+  </si>
+  <si>
+    <t>Acute systolic and diastolic blood pressure recovery responses to heavy resistance exercise followed by manual massage or pneumatic compression in women</t>
+  </si>
+  <si>
+    <t>Functional Status and Cardiac Rehabilitation Barriers Predict One-Year Outcomes After Acute Coronary Syndrome</t>
+  </si>
+  <si>
+    <t>Pulmonary Function in Adults with Severe Eosinophilic Asthma Using Biologicals: A Case-Control Study</t>
+  </si>
+  <si>
+    <t>10.12865/CHSJ.52.02.07</t>
+  </si>
+  <si>
+    <t>Intramedullary injection of polymerized laminin in acute traumatic spinal cord injury: a first-in-human pilot study</t>
+  </si>
+  <si>
+    <t>10.1038/s41393-026-01238-6</t>
+  </si>
+  <si>
+    <t>Medidas de area seccional transversa, índice de ecogenicidade e distância pele-nervo do nervo ciático em assintomáticos- estudo de confiabilidade</t>
+  </si>
+  <si>
+    <t>Posture and postural balance in people aged 6-39 years with asthma: a systematic review</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.186575.1</t>
+  </si>
+  <si>
+    <t>Intervertebral Lumbar Space and Sciatic Nerve Thickness During Flexion-Distraction Technique in Asymptomatic Participants - An Exploratory Study</t>
+  </si>
+  <si>
+    <t>Demographic and psychosocial states associated with inefficient conditioned pain modulation in individuals with and without musculoskeletal pain</t>
+  </si>
+  <si>
+    <t>Prognostic factors of future disability following recovery from na episode of low back pain</t>
+  </si>
+  <si>
+    <t>Effect of high-intensity interval training (HIIT) versus moderate-intensity continuous training (MICT) on insulin sensitivity in participants with type 2 diabetes mellitus (T2DM): A systematic review and meta-analysis of randomised controlled trials</t>
+  </si>
+  <si>
+    <t>Hand preference shows limited influence on the magnitude but modulates the directional organization of upright posture control during a reaching and grasping task: a cross-sectional study in healthy women</t>
+  </si>
+  <si>
+    <t>Pain and injury prevalence and their associations with psychosocial and motivational factors in amateur beach tennis players: a cross‑sectional study</t>
+  </si>
+  <si>
+    <t>10.1007/s11332-026-01895-3</t>
+  </si>
+  <si>
+    <t>10.1016/j.jpain.2026.106422</t>
+  </si>
+  <si>
+    <t>10.21091/mppa.2026.03011</t>
+  </si>
+  <si>
+    <t>Post-tuberculosis lung disease: functional impairment assessed by respiratory oscillometry, muscle strength and exercise capacity</t>
+  </si>
+  <si>
+    <t>Balance Control and its Correlation with Functional Capacity in People with Post-Tuberculosis Lung Disease</t>
+  </si>
+  <si>
+    <t>10.1097/PHM.0000000000002932</t>
+  </si>
+  <si>
+    <t>Effects of Differing Nutritional Supplementation Combined With High-Intensity Aerobic Interval Training on Functional Exercise Capacity, Cardiac Function, and Quality of Life in Patients With Heart Failure and Reduced Ejection Fraction A Randomized Trial</t>
+  </si>
+  <si>
+    <t>Translation, cross-cultural adaptation and measurement properties of the Brazilian Portuguese version of the central aspects of pain in the knee in individuals with knee osteoarthritis</t>
+  </si>
+  <si>
+    <t>10.1016/j.bjpt.2026.101655</t>
+  </si>
+  <si>
+    <t>Back Beliefs Questionnaire: A cross-cultural measurement study</t>
+  </si>
+  <si>
+    <t>10.1016/j.msksp.2026.103663</t>
+  </si>
+  <si>
+    <t>10.3390/muscles5030064</t>
+  </si>
+  <si>
+    <t>10.1016/j.chstcc.2026.100332</t>
+  </si>
+  <si>
+    <t>Discriminative Performance of Four Bedside Methods for Predicting PEEP Response in Severe ARDS</t>
   </si>
 </sst>
 </file>
@@ -5269,7 +5377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I674"/>
+  <dimension ref="A1:I692"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12196,10 +12304,10 @@
         <v>2025</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
@@ -12251,7 +12359,7 @@
         <v>2026</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C636" s="3" t="s">
         <v>1486</v>
@@ -12262,10 +12370,10 @@
         <v>2026</v>
       </c>
       <c r="B637" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C637" s="3" t="s">
         <v>1535</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
@@ -12273,10 +12381,10 @@
         <v>2026</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1540</v>
+        <v>1558</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1539</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
@@ -12284,10 +12392,10 @@
         <v>2026</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1528</v>
+        <v>1570</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1527</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
@@ -12295,10 +12403,10 @@
         <v>2026</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>1411</v>
+        <v>1596</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1412</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.2">
@@ -12306,10 +12414,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1553</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12317,10 +12425,10 @@
         <v>2026</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1491</v>
+        <v>1568</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>1484</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
@@ -12328,10 +12436,10 @@
         <v>2026</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1505</v>
+        <v>1588</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>1493</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
@@ -12339,10 +12447,10 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12350,10 +12458,10 @@
         <v>2026</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1545</v>
+        <v>1411</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1546</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
@@ -12361,10 +12469,10 @@
         <v>2026</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>1497</v>
+        <v>1564</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1496</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
@@ -12372,10 +12480,10 @@
         <v>2026</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1538</v>
+        <v>1550</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1523</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
@@ -12383,10 +12491,10 @@
         <v>2026</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1363</v>
+        <v>1591</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1362</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
@@ -12394,10 +12502,10 @@
         <v>2026</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1530</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
@@ -12405,10 +12513,10 @@
         <v>2026</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>1420</v>
+        <v>1491</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1419</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
@@ -12416,10 +12524,10 @@
         <v>2026</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1529</v>
+        <v>1505</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1524</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
@@ -12427,10 +12535,10 @@
         <v>2026</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>1494</v>
+        <v>1532</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1495</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
@@ -12438,10 +12546,10 @@
         <v>2026</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1408</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
@@ -12449,10 +12557,10 @@
         <v>2026</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C654" s="19" t="s">
-        <v>1549</v>
+        <v>1543</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1544</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12460,10 +12568,10 @@
         <v>2026</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1502</v>
+        <v>1541</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>1503</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
@@ -12471,10 +12579,10 @@
         <v>2026</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>1514</v>
+        <v>1497</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>1515</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
@@ -12482,10 +12590,10 @@
         <v>2026</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1521</v>
+        <v>1576</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>1520</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
@@ -12493,10 +12601,10 @@
         <v>2026</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>1409</v>
+        <v>1537</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>1410</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
@@ -12504,10 +12612,10 @@
         <v>2026</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>1525</v>
+        <v>1363</v>
       </c>
       <c r="C659" s="3" t="s">
-        <v>1526</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
@@ -12515,10 +12623,10 @@
         <v>2026</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>1555</v>
+        <v>1531</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>1554</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
@@ -12526,10 +12634,10 @@
         <v>2026</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1487</v>
+        <v>1562</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>1425</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
@@ -12537,78 +12645,87 @@
         <v>2026</v>
       </c>
       <c r="B662" s="3" t="s">
-        <v>1561</v>
+        <v>1586</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1562</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A663" s="15" t="s">
-        <v>0</v>
+      <c r="A663" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B663" s="3" t="s">
+        <v>1420</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>1237</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A664" s="15" t="s">
-        <v>0</v>
+      <c r="A664" s="15">
+        <v>2026</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>1372</v>
+        <v>1529</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1490</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A665" s="15" t="s">
-        <v>0</v>
+      <c r="A665" s="15">
+        <v>2026</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>1544</v>
+        <v>1494</v>
       </c>
       <c r="C665" s="3" t="s">
-        <v>1522</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A666" s="15" t="s">
-        <v>0</v>
+      <c r="A666" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>1579</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1534</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A667" s="15" t="s">
-        <v>0</v>
+      <c r="A667" s="15">
+        <v>2026</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="C667" s="3" t="s">
-        <v>1541</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A668" s="15" t="s">
-        <v>0</v>
+      <c r="A668" s="15">
+        <v>2026</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>1516</v>
-      </c>
-      <c r="C668" s="3" t="s">
-        <v>1517</v>
+        <v>1548</v>
+      </c>
+      <c r="C668" s="19" t="s">
+        <v>1547</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A669" s="15" t="s">
-        <v>0</v>
+      <c r="A669" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>1574</v>
       </c>
       <c r="C669" s="3" t="s">
-        <v>1556</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
@@ -12616,48 +12733,237 @@
         <v>2026</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>1557</v>
+        <v>1502</v>
       </c>
       <c r="C670" s="3" t="s">
-        <v>1543</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A671" s="15" t="s">
+      <c r="A671" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A672" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A673" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A674" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A675" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B675" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A676" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A677" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A678" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A679" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C671" s="3" t="s">
-        <v>1558</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A672" s="15" t="s">
+      <c r="C679" s="3" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A680" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C672" s="3" t="s">
-        <v>1559</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A673" s="15" t="s">
+      <c r="C680" s="3" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A681" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A682" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C673" s="3" t="s">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A674" s="15" t="s">
+      <c r="B682" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A683" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C674" s="3" t="s">
-        <v>1563</v>
+      <c r="C683" s="3" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A684" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A685" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B685" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A686" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C686" s="18" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A687" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A688" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A689" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A690" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A691" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B691" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A692" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1555</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C668">
-    <sortCondition ref="A2:A668"/>
-    <sortCondition ref="C2:C668"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C692">
+    <sortCondition ref="A2:A692"/>
+    <sortCondition ref="C2:C692"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">
